--- a/Results/pairwise_wilcoxon_tests.xlsx
+++ b/Results/pairwise_wilcoxon_tests.xlsx
@@ -444,13 +444,13 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>0.845703125</v>
+        <v>0.02734375</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0.765625</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
@@ -464,10 +464,10 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>0.275390625</v>
+        <v>0.046875</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -484,13 +484,13 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>0.10546875</v>
+        <v>0.009765625</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0.2734375</v>
       </c>
       <c r="F4" t="b">
         <v>0</v>
@@ -504,13 +504,13 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D5">
-        <v>0.02734375</v>
+        <v>0.845703125</v>
       </c>
       <c r="E5">
-        <v>0.765625</v>
+        <v>1</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
@@ -524,10 +524,10 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6">
-        <v>0.556640625</v>
+        <v>0.4921875</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -544,10 +544,10 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D7">
-        <v>0.07421875</v>
+        <v>0.10546875</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -564,10 +564,10 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D8">
-        <v>0.064453125</v>
+        <v>0.130859375</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -584,10 +584,10 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D9">
-        <v>0.193359375</v>
+        <v>0.10546875</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -604,10 +604,10 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D10">
-        <v>0.09765625</v>
+        <v>0.6953125</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -624,13 +624,13 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="D11">
-        <v>0.005859375</v>
+        <v>0.009765625</v>
       </c>
       <c r="E11">
-        <v>0.1640625</v>
+        <v>0.2734375</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
@@ -644,13 +644,13 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0.02734375</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0.765625</v>
       </c>
       <c r="F12" t="b">
         <v>0</v>
@@ -664,13 +664,13 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D13">
-        <v>0.01953125</v>
+        <v>0.048828125</v>
       </c>
       <c r="E13">
-        <v>0.546875</v>
+        <v>1</v>
       </c>
       <c r="F13" t="b">
         <v>0</v>
@@ -684,13 +684,13 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D14">
-        <v>0.01953125</v>
+        <v>0.083984375</v>
       </c>
       <c r="E14">
-        <v>0.546875</v>
+        <v>1</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
@@ -704,13 +704,13 @@
         <v>9</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D15">
-        <v>0.01953125</v>
+        <v>0.16015625</v>
       </c>
       <c r="E15">
-        <v>0.546875</v>
+        <v>1</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
@@ -724,10 +724,10 @@
         <v>10</v>
       </c>
       <c r="C16">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D16">
-        <v>0.09375</v>
+        <v>0.431640625</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -744,10 +744,10 @@
         <v>11</v>
       </c>
       <c r="C17">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D17">
-        <v>0.375</v>
+        <v>0.037109375</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -764,10 +764,10 @@
         <v>12</v>
       </c>
       <c r="C18">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D18">
-        <v>0.193359375</v>
+        <v>0.921875</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -784,10 +784,10 @@
         <v>13</v>
       </c>
       <c r="C19">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D19">
-        <v>0.232421875</v>
+        <v>0.921875</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -804,13 +804,13 @@
         <v>10</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D20">
-        <v>0.00390625</v>
+        <v>0.01953125</v>
       </c>
       <c r="E20">
-        <v>0.109375</v>
+        <v>0.546875</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
@@ -824,13 +824,13 @@
         <v>11</v>
       </c>
       <c r="C21">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D21">
-        <v>0.10546875</v>
+        <v>0.01953125</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0.546875</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
@@ -844,13 +844,13 @@
         <v>12</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D22">
-        <v>0.00390625</v>
+        <v>0.193359375</v>
       </c>
       <c r="E22">
-        <v>0.109375</v>
+        <v>1</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
@@ -864,13 +864,13 @@
         <v>13</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D23">
-        <v>0.00390625</v>
+        <v>0.01953125</v>
       </c>
       <c r="E23">
-        <v>0.109375</v>
+        <v>0.546875</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
@@ -884,13 +884,13 @@
         <v>11</v>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D24">
-        <v>0.02734375</v>
+        <v>0.921875</v>
       </c>
       <c r="E24">
-        <v>0.765625</v>
+        <v>1</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
@@ -904,10 +904,10 @@
         <v>12</v>
       </c>
       <c r="C25">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D25">
-        <v>0.845703125</v>
+        <v>0.359375</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -924,10 +924,10 @@
         <v>13</v>
       </c>
       <c r="C26">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D26">
-        <v>0.921875</v>
+        <v>0.140625</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -944,10 +944,10 @@
         <v>12</v>
       </c>
       <c r="C27">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D27">
-        <v>0.083984375</v>
+        <v>0.16015625</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -964,10 +964,10 @@
         <v>13</v>
       </c>
       <c r="C28">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D28">
-        <v>0.064453125</v>
+        <v>0.193359375</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -984,10 +984,10 @@
         <v>13</v>
       </c>
       <c r="C29">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D29">
-        <v>0.845703125</v>
+        <v>0.900390625</v>
       </c>
       <c r="E29">
         <v>1</v>
